--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-08-08.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-08-08.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_1B1D3D9757D9E61ED31A3611595ED87656CD7710" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8C2115C-88C1-47BF-A7E5-F19B92EA7163}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_1B1D3D9757D9E61ED31A3611595ED87656CD7710" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5010E52C-513F-4F28-938C-ECDD259B92CD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sinais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -670,6 +683,10 @@
       <c r="K2">
         <v>1.72</v>
       </c>
+      <c r="L2" t="str">
+        <f>IF(O2=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
+      </c>
       <c r="N2" t="s">
         <v>20</v>
       </c>
@@ -711,6 +728,10 @@
       <c r="K3">
         <v>1.47</v>
       </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L16" si="0">IF(O3=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
+      </c>
       <c r="N3" t="s">
         <v>20</v>
       </c>
@@ -752,6 +773,10 @@
       <c r="K4">
         <v>1.35</v>
       </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N4" t="s">
         <v>20</v>
       </c>
@@ -793,6 +818,10 @@
       <c r="K5">
         <v>2.27</v>
       </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N5" t="s">
         <v>20</v>
       </c>
@@ -834,6 +863,10 @@
       <c r="K6">
         <v>2.27</v>
       </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N6" t="s">
         <v>20</v>
       </c>
@@ -875,6 +908,10 @@
       <c r="K7">
         <v>1.43</v>
       </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N7" t="s">
         <v>20</v>
       </c>
@@ -916,6 +953,10 @@
       <c r="K8">
         <v>1.56</v>
       </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N8" t="s">
         <v>20</v>
       </c>
@@ -957,6 +998,10 @@
       <c r="K9">
         <v>1.32</v>
       </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N9" t="s">
         <v>20</v>
       </c>
@@ -998,8 +1043,15 @@
       <c r="K10">
         <v>1.85</v>
       </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N10" t="s">
         <v>20</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1036,6 +1088,10 @@
       <c r="K11">
         <v>1.67</v>
       </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N11" t="s">
         <v>20</v>
       </c>
@@ -1077,6 +1133,10 @@
       <c r="K12">
         <v>1.32</v>
       </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N12" t="s">
         <v>20</v>
       </c>
@@ -1118,8 +1178,15 @@
       <c r="K13">
         <v>1.47</v>
       </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N13" t="s">
         <v>20</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1156,6 +1223,10 @@
       <c r="K14">
         <v>1.67</v>
       </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N14" t="s">
         <v>20</v>
       </c>
@@ -1197,8 +1268,15 @@
       <c r="K15">
         <v>1.79</v>
       </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="N15" t="s">
         <v>20</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1234,6 +1312,10 @@
       </c>
       <c r="K16">
         <v>2</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="N16" t="s">
         <v>20</v>
